--- a/tests/Kookerella.CsOpenXmlDsl.Tests/Examples/FrozenPanes/output.xlsx
+++ b/tests/Kookerella.CsOpenXmlDsl.Tests/Examples/FrozenPanes/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R0394fc62eb474e6c"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Rc83b1d1768c04eb1"/>
   </x:sheets>
 </x:workbook>
 </file>

--- a/tests/Kookerella.CsOpenXmlDsl.Tests/Examples/FrozenPanes/output.xlsx
+++ b/tests/Kookerella.CsOpenXmlDsl.Tests/Examples/FrozenPanes/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Rc83b1d1768c04eb1"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Rdaf6b56b1b484aff"/>
   </x:sheets>
 </x:workbook>
 </file>

--- a/tests/Kookerella.CsOpenXmlDsl.Tests/Examples/FrozenPanes/output.xlsx
+++ b/tests/Kookerella.CsOpenXmlDsl.Tests/Examples/FrozenPanes/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Rdaf6b56b1b484aff"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R3aeca2e175bc4fca"/>
   </x:sheets>
 </x:workbook>
 </file>

--- a/tests/Kookerella.CsOpenXmlDsl.Tests/Examples/FrozenPanes/output.xlsx
+++ b/tests/Kookerella.CsOpenXmlDsl.Tests/Examples/FrozenPanes/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R3aeca2e175bc4fca"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Rfb7f017b61564d18"/>
   </x:sheets>
 </x:workbook>
 </file>

--- a/tests/Kookerella.CsOpenXmlDsl.Tests/Examples/FrozenPanes/output.xlsx
+++ b/tests/Kookerella.CsOpenXmlDsl.Tests/Examples/FrozenPanes/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Rfb7f017b61564d18"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Re7ce94a179cb49c2"/>
   </x:sheets>
 </x:workbook>
 </file>

--- a/tests/Kookerella.CsOpenXmlDsl.Tests/Examples/FrozenPanes/output.xlsx
+++ b/tests/Kookerella.CsOpenXmlDsl.Tests/Examples/FrozenPanes/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Re7ce94a179cb49c2"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Rc2e0b77a395143cf"/>
   </x:sheets>
 </x:workbook>
 </file>

--- a/tests/Kookerella.CsOpenXmlDsl.Tests/Examples/FrozenPanes/output.xlsx
+++ b/tests/Kookerella.CsOpenXmlDsl.Tests/Examples/FrozenPanes/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Rc2e0b77a395143cf"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Radb56ea7e07843db"/>
   </x:sheets>
 </x:workbook>
 </file>

--- a/tests/Kookerella.CsOpenXmlDsl.Tests/Examples/FrozenPanes/output.xlsx
+++ b/tests/Kookerella.CsOpenXmlDsl.Tests/Examples/FrozenPanes/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Radb56ea7e07843db"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R1be20016ea4e414c"/>
   </x:sheets>
 </x:workbook>
 </file>

--- a/tests/Kookerella.CsOpenXmlDsl.Tests/Examples/FrozenPanes/output.xlsx
+++ b/tests/Kookerella.CsOpenXmlDsl.Tests/Examples/FrozenPanes/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R1be20016ea4e414c"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Re94e72e95af746d0"/>
   </x:sheets>
 </x:workbook>
 </file>

--- a/tests/Kookerella.CsOpenXmlDsl.Tests/Examples/FrozenPanes/output.xlsx
+++ b/tests/Kookerella.CsOpenXmlDsl.Tests/Examples/FrozenPanes/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Re94e72e95af746d0"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Rdb6583ef7ccb4293"/>
   </x:sheets>
 </x:workbook>
 </file>

--- a/tests/Kookerella.CsOpenXmlDsl.Tests/Examples/FrozenPanes/output.xlsx
+++ b/tests/Kookerella.CsOpenXmlDsl.Tests/Examples/FrozenPanes/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Rdb6583ef7ccb4293"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R5d82703b9ae34359"/>
   </x:sheets>
 </x:workbook>
 </file>

--- a/tests/Kookerella.CsOpenXmlDsl.Tests/Examples/FrozenPanes/output.xlsx
+++ b/tests/Kookerella.CsOpenXmlDsl.Tests/Examples/FrozenPanes/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R5d82703b9ae34359"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Rbb6e08ec4d834722"/>
   </x:sheets>
 </x:workbook>
 </file>

--- a/tests/Kookerella.CsOpenXmlDsl.Tests/Examples/FrozenPanes/output.xlsx
+++ b/tests/Kookerella.CsOpenXmlDsl.Tests/Examples/FrozenPanes/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Rbb6e08ec4d834722"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R45f7febd26ad48ed"/>
   </x:sheets>
 </x:workbook>
 </file>

--- a/tests/Kookerella.CsOpenXmlDsl.Tests/Examples/FrozenPanes/output.xlsx
+++ b/tests/Kookerella.CsOpenXmlDsl.Tests/Examples/FrozenPanes/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R45f7febd26ad48ed"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R6ce5a24dca914374"/>
   </x:sheets>
 </x:workbook>
 </file>
